--- a/resources/templates/karaba/deregistration_application.xlsx
+++ b/resources/templates/karaba/deregistration_application.xlsx
@@ -295,7 +295,7 @@
     <t>길영채</t>
   </si>
   <si>
-    <t>731110-1041111</t>
+    <t>010-4703-0627</t>
   </si>
 </sst>
 </file>
